--- a/Excel/ISA Documentation.xlsx
+++ b/Excel/ISA Documentation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ProtoCore\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thega\Projects\ProtoCore\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D452019B-7919-441A-BACD-1751147EE9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C449C9B1-5A17-41B4-997B-A5B321448611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
-  <si>
-    <t>RISC CORE ISA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
   <si>
     <t>Format:</t>
   </si>
@@ -164,12 +161,6 @@
     <t>x(RA + DATA) = RB</t>
   </si>
   <si>
-    <t>Examples</t>
-  </si>
-  <si>
-    <t>ADD 3 = R1+R2</t>
-  </si>
-  <si>
     <t>0000</t>
   </si>
   <si>
@@ -203,85 +194,88 @@
     <t>1010</t>
   </si>
   <si>
-    <t>0000_0001_0010_0011_00000000</t>
-  </si>
-  <si>
-    <t>1011_0000_0011_0000_00000011</t>
-  </si>
-  <si>
-    <t>1010_0000_0000_0001_00000000</t>
-  </si>
-  <si>
-    <t>1010_0000_0000_0010_00000001</t>
-  </si>
-  <si>
     <t>RD</t>
   </si>
   <si>
-    <t>1010_0000_0000_0001_00000100</t>
-  </si>
-  <si>
-    <t>load 1 = x(0+0)</t>
-  </si>
-  <si>
-    <t>load 2 = x(0+1)</t>
-  </si>
-  <si>
-    <t>STORE x(0+3) = R3</t>
-  </si>
-  <si>
-    <t>1000_0001_0000_0010_00000101</t>
-  </si>
-  <si>
-    <t>LOAD 1 = x(0+4)</t>
-  </si>
-  <si>
-    <t>ADDI R2 = R1+5</t>
-  </si>
-  <si>
-    <t>1011_0000_0010_0000_00001000</t>
-  </si>
-  <si>
-    <t>STORE x(0+8) = R2</t>
-  </si>
-  <si>
-    <t>1100_0001_0010_0000_00000010</t>
-  </si>
-  <si>
-    <t>BEQ R1==R2 +2</t>
-  </si>
-  <si>
-    <t>0001_0001_0010_0011_00000000</t>
-  </si>
-  <si>
-    <t>R3=R1-R2</t>
-  </si>
-  <si>
-    <t>1110_0000_0000_0000_00000111</t>
-  </si>
-  <si>
-    <t>JMP 7</t>
-  </si>
-  <si>
-    <t>1111_0000_0000_0000_00000000</t>
-  </si>
-  <si>
     <t>PC = RA + DATA</t>
   </si>
   <si>
-    <t>(or immediate jump with R0 + DATA)</t>
-  </si>
-  <si>
     <t>(signed DATA)</t>
   </si>
   <si>
     <t xml:space="preserve">NOTE: </t>
   </si>
   <si>
-    <t>FFF000 and FFFF00 are reserved words in the CPU, and are used in the ROM_FLASHING program to signify the end of transmission of new words. As of now</t>
-  </si>
-  <si>
-    <t>these words are illegal syntax, and cannot be created regardless, but if these are somehow created and flashed in accidentally, the flash will terminate early.</t>
+    <t>FFF000 and FFFF00 are reserved instructions in the CPU, and are used in the ROM_FLASHING program to signify the end of transmission of new instructions. As of now</t>
+  </si>
+  <si>
+    <t>these instructions are illegal syntax, and cannot be created regardless, but if these are somehow created and flashed in accidentally, the flash will terminate early.</t>
+  </si>
+  <si>
+    <t>ProtoCore SoC ISA</t>
+  </si>
+  <si>
+    <t>format:</t>
+  </si>
+  <si>
+    <t>ADD RD, RA, RB</t>
+  </si>
+  <si>
+    <t>SUB RD, RA, RB</t>
+  </si>
+  <si>
+    <t>AND RD, RA, RB</t>
+  </si>
+  <si>
+    <t>OR RD, RA, RB</t>
+  </si>
+  <si>
+    <t>XOR RD, RA, RB</t>
+  </si>
+  <si>
+    <t>NOT RD, RA</t>
+  </si>
+  <si>
+    <t>SHL RD, RA</t>
+  </si>
+  <si>
+    <t>SHR RD, RA</t>
+  </si>
+  <si>
+    <t>ADDI RD, RA, DATA</t>
+  </si>
+  <si>
+    <t>ANDI RD, RA, DATA</t>
+  </si>
+  <si>
+    <t>LOAD RD, RA, DATA</t>
+  </si>
+  <si>
+    <t>STORE RA, RB, DATA</t>
+  </si>
+  <si>
+    <t>BEQ RA, RB, DATA</t>
+  </si>
+  <si>
+    <t>BNE RA, RB, DATA</t>
+  </si>
+  <si>
+    <t>JMP RA, DATA</t>
+  </si>
+  <si>
+    <t>Considerations:</t>
+  </si>
+  <si>
+    <t>Add single-cycle macros, specializing different instructions more (such as JMP -&gt; JMP / JMPI)</t>
+  </si>
+  <si>
+    <t>Add macros to expand ruleset to include 2-cycle ops, such as ORI</t>
+  </si>
+  <si>
+    <t>Carry Flag functionality</t>
+  </si>
+  <si>
+    <t>Sub-Opcode functionality (such as the RD, RA, and RB sections of the HALT opcode)</t>
   </si>
 </sst>
 </file>
@@ -654,418 +648,343 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3793813-9B20-438F-90FC-3E0D3543C5BE}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1110</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1111</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
         <v>57</v>
       </c>
-      <c r="H2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="G7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
-      <c r="G10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" t="s">
-        <v>69</v>
-      </c>
-      <c r="H15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" t="s">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>75</v>
       </c>
-      <c r="H18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1011</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1100</v>
-      </c>
-      <c r="D24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="1">
-        <v>1101</v>
-      </c>
-      <c r="D25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>79</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="B12:B22" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/Excel/ISA Documentation.xlsx
+++ b/Excel/ISA Documentation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thega\Projects\ProtoCore\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ProtoCore\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C449C9B1-5A17-41B4-997B-A5B321448611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68CC77C9-0E98-4100-90B7-2618D34C12A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="90">
   <si>
     <t>Format:</t>
   </si>
@@ -203,15 +203,6 @@
     <t>(signed DATA)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOTE: </t>
-  </si>
-  <si>
-    <t>FFF000 and FFFF00 are reserved instructions in the CPU, and are used in the ROM_FLASHING program to signify the end of transmission of new instructions. As of now</t>
-  </si>
-  <si>
-    <t>these instructions are illegal syntax, and cannot be created regardless, but if these are somehow created and flashed in accidentally, the flash will terminate early.</t>
-  </si>
-  <si>
     <t>ProtoCore SoC ISA</t>
   </si>
   <si>
@@ -276,6 +267,45 @@
   </si>
   <si>
     <t>Sub-Opcode functionality (such as the RD, RA, and RB sections of the HALT opcode)</t>
+  </si>
+  <si>
+    <t>Reserved Instructions:</t>
+  </si>
+  <si>
+    <t>FFFF00</t>
+  </si>
+  <si>
+    <t>FFF000</t>
+  </si>
+  <si>
+    <t>FFE000</t>
+  </si>
+  <si>
+    <t>FFD000</t>
+  </si>
+  <si>
+    <t>FF0000</t>
+  </si>
+  <si>
+    <t>Start memory load process</t>
+  </si>
+  <si>
+    <t>Stop memory load process without PC reset</t>
+  </si>
+  <si>
+    <t>Stop memory load process with PC reset</t>
+  </si>
+  <si>
+    <t>Set MMIO display mode</t>
+  </si>
+  <si>
+    <t>Set REG display mode</t>
+  </si>
+  <si>
+    <t>MMIO Display:</t>
+  </si>
+  <si>
+    <t>The 16 bit LED display corresponds to registers 255 and 254 of the ram module. Upon update of the x255 location, the display will update.</t>
   </si>
 </sst>
 </file>
@@ -648,26 +678,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3793813-9B20-438F-90FC-3E0D3543C5BE}">
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -684,7 +714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -701,7 +731,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -709,13 +739,13 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -723,13 +753,13 @@
         <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -737,13 +767,13 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -751,13 +781,13 @@
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -765,13 +795,13 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -779,13 +809,13 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -793,13 +823,13 @@
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -807,13 +837,13 @@
         <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -821,13 +851,13 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -835,13 +865,13 @@
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -849,13 +879,13 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -863,13 +893,13 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -877,13 +907,13 @@
         <v>1011</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -891,7 +921,7 @@
         <v>1100</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G19" t="s">
         <v>37</v>
@@ -900,7 +930,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -908,7 +938,7 @@
         <v>1101</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
         <v>38</v>
@@ -917,7 +947,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -925,13 +955,13 @@
         <v>1110</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -945,42 +975,84 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
       <c r="B25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ISA Documentation.xlsx
+++ b/Excel/ISA Documentation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ProtoCore\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68CC77C9-0E98-4100-90B7-2618D34C12A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516B656F-C37B-4A8E-B25D-FB2F5C774157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
   <si>
     <t>Format:</t>
   </si>
@@ -269,53 +269,98 @@
     <t>Sub-Opcode functionality (such as the RD, RA, and RB sections of the HALT opcode)</t>
   </si>
   <si>
-    <t>Reserved Instructions:</t>
-  </si>
-  <si>
-    <t>FFFF00</t>
-  </si>
-  <si>
-    <t>FFF000</t>
-  </si>
-  <si>
-    <t>FFE000</t>
-  </si>
-  <si>
-    <t>FFD000</t>
-  </si>
-  <si>
-    <t>FF0000</t>
-  </si>
-  <si>
-    <t>Start memory load process</t>
-  </si>
-  <si>
-    <t>Stop memory load process without PC reset</t>
-  </si>
-  <si>
-    <t>Stop memory load process with PC reset</t>
-  </si>
-  <si>
-    <t>Set MMIO display mode</t>
-  </si>
-  <si>
-    <t>Set REG display mode</t>
-  </si>
-  <si>
     <t>MMIO Display:</t>
   </si>
   <si>
     <t>The 16 bit LED display corresponds to registers 255 and 254 of the ram module. Upon update of the x255 location, the display will update.</t>
+  </si>
+  <si>
+    <t>System Commands</t>
+  </si>
+  <si>
+    <t>0xF1</t>
+  </si>
+  <si>
+    <t>0xF2</t>
+  </si>
+  <si>
+    <t>0xF3</t>
+  </si>
+  <si>
+    <t>0xF4</t>
+  </si>
+  <si>
+    <t>0xF5</t>
+  </si>
+  <si>
+    <t>0xF7</t>
+  </si>
+  <si>
+    <t>0xF8</t>
+  </si>
+  <si>
+    <t>0xF9</t>
+  </si>
+  <si>
+    <t>0xFA</t>
+  </si>
+  <si>
+    <t>0xFB</t>
+  </si>
+  <si>
+    <t>0xFC</t>
+  </si>
+  <si>
+    <t>0xFD</t>
+  </si>
+  <si>
+    <t>0xFE</t>
+  </si>
+  <si>
+    <t>0xFF</t>
+  </si>
+  <si>
+    <t>Begin UART programming</t>
+  </si>
+  <si>
+    <t>End uart programming, keep PC</t>
+  </si>
+  <si>
+    <t>End uart programming, reset PC</t>
+  </si>
+  <si>
+    <t>MMIO Display</t>
+  </si>
+  <si>
+    <t>REG display</t>
+  </si>
+  <si>
+    <t>0xF6 XX</t>
+  </si>
+  <si>
+    <t>DEBUG mode (00: normal, 01: Step)</t>
+  </si>
+  <si>
+    <t>Reset CPU</t>
+  </si>
+  <si>
+    <t>Step PC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -678,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3793813-9B20-438F-90FC-3E0D3543C5BE}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="27" customWidth="1"/>
@@ -686,18 +731,18 @@
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -714,7 +759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -731,7 +776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -744,8 +789,11 @@
       <c r="G6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -758,8 +806,14 @@
       <c r="G7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -772,8 +826,14 @@
       <c r="G8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -786,8 +846,14 @@
       <c r="G9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -800,8 +866,14 @@
       <c r="G10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -814,8 +886,14 @@
       <c r="G11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -828,8 +906,14 @@
       <c r="G12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -842,8 +926,14 @@
       <c r="G13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -856,8 +946,14 @@
       <c r="G14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -870,8 +966,11 @@
       <c r="G15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -884,8 +983,11 @@
       <c r="G16" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -898,8 +1000,11 @@
       <c r="G17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -912,8 +1017,11 @@
       <c r="G18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -929,8 +1037,11 @@
       <c r="H19" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -946,8 +1057,11 @@
       <c r="H20" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -960,8 +1074,11 @@
       <c r="G21" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -975,87 +1092,43 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>78</v>
       </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Excel/ISA Documentation.xlsx
+++ b/Excel/ISA Documentation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ProtoCore\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thega\Projects\ProtoCore\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516B656F-C37B-4A8E-B25D-FB2F5C774157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB21B461-A753-42B0-9FE5-630384B49476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
   <si>
     <t>Format:</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>Step PC</t>
+  </si>
+  <si>
+    <t>HALT DATA</t>
   </si>
 </sst>
 </file>
@@ -724,25 +727,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3793813-9B20-438F-90FC-3E0D3543C5BE}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -759,7 +762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -776,7 +779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -793,7 +796,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -813,7 +816,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -833,7 +836,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -853,7 +856,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -873,7 +876,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -893,7 +896,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -913,7 +916,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -933,7 +936,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -953,7 +956,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -970,7 +973,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -987,7 +990,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1004,7 +1007,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1021,7 +1024,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1041,7 +1044,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1061,7 +1064,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1078,7 +1081,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1086,43 +1089,43 @@
         <v>1111</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="G22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>76</v>
       </c>

--- a/Excel/ISA Documentation.xlsx
+++ b/Excel/ISA Documentation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thega\Projects\ProtoCore\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ProtoCore\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB21B461-A753-42B0-9FE5-630384B49476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC67595-03DC-4246-9ACD-EDB97874E690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="153">
   <si>
     <t>Format:</t>
   </si>
@@ -50,9 +50,6 @@
     <t>RB</t>
   </si>
   <si>
-    <t>DATA</t>
-  </si>
-  <si>
     <t>4 bits</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>STORE</t>
   </si>
   <si>
-    <t>opcodes:</t>
-  </si>
-  <si>
     <t>bin:</t>
   </si>
   <si>
@@ -140,27 +134,6 @@
     <t>RD = RA &gt;&gt; 1</t>
   </si>
   <si>
-    <t>RD = RA + DATA</t>
-  </si>
-  <si>
-    <t>RD = RA &amp; DATA</t>
-  </si>
-  <si>
-    <t>RD = x(RA+DATA)</t>
-  </si>
-  <si>
-    <t>if RA = RB then PC += DATA</t>
-  </si>
-  <si>
-    <t>if RA ~= RB then PC += DATA</t>
-  </si>
-  <si>
-    <t>stop execution</t>
-  </si>
-  <si>
-    <t>x(RA + DATA) = RB</t>
-  </si>
-  <si>
     <t>0000</t>
   </si>
   <si>
@@ -197,12 +170,6 @@
     <t>RD</t>
   </si>
   <si>
-    <t>PC = RA + DATA</t>
-  </si>
-  <si>
-    <t>(signed DATA)</t>
-  </si>
-  <si>
     <t>ProtoCore SoC ISA</t>
   </si>
   <si>
@@ -233,36 +200,9 @@
     <t>SHR RD, RA</t>
   </si>
   <si>
-    <t>ADDI RD, RA, DATA</t>
-  </si>
-  <si>
-    <t>ANDI RD, RA, DATA</t>
-  </si>
-  <si>
-    <t>LOAD RD, RA, DATA</t>
-  </si>
-  <si>
-    <t>STORE RA, RB, DATA</t>
-  </si>
-  <si>
-    <t>BEQ RA, RB, DATA</t>
-  </si>
-  <si>
-    <t>BNE RA, RB, DATA</t>
-  </si>
-  <si>
-    <t>JMP RA, DATA</t>
-  </si>
-  <si>
     <t>Considerations:</t>
   </si>
   <si>
-    <t>Add single-cycle macros, specializing different instructions more (such as JMP -&gt; JMP / JMPI)</t>
-  </si>
-  <si>
-    <t>Add macros to expand ruleset to include 2-cycle ops, such as ORI</t>
-  </si>
-  <si>
     <t>Carry Flag functionality</t>
   </si>
   <si>
@@ -347,14 +287,221 @@
     <t>Step PC</t>
   </si>
   <si>
-    <t>HALT DATA</t>
+    <t>NOP</t>
+  </si>
+  <si>
+    <t>MOV</t>
+  </si>
+  <si>
+    <t>CLR</t>
+  </si>
+  <si>
+    <t>INC</t>
+  </si>
+  <si>
+    <t>DEC</t>
+  </si>
+  <si>
+    <t>NEG</t>
+  </si>
+  <si>
+    <t>RJMP</t>
+  </si>
+  <si>
+    <t>BEQZ</t>
+  </si>
+  <si>
+    <t>BNEZ</t>
+  </si>
+  <si>
+    <t>LDI</t>
+  </si>
+  <si>
+    <t>JMPA</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>CLR RD</t>
+  </si>
+  <si>
+    <t>INC RD</t>
+  </si>
+  <si>
+    <t>DEC RD</t>
+  </si>
+  <si>
+    <t>NEG RD</t>
+  </si>
+  <si>
+    <t>MOV RD, RA</t>
+  </si>
+  <si>
+    <t>RJMP IMM</t>
+  </si>
+  <si>
+    <t>BEQZ RA, IMM</t>
+  </si>
+  <si>
+    <t>BNEZ RA, IMM</t>
+  </si>
+  <si>
+    <t>LDI RD, IMM</t>
+  </si>
+  <si>
+    <t>IMM</t>
+  </si>
+  <si>
+    <t>ADDI RD, RA, IMM</t>
+  </si>
+  <si>
+    <t>RD = RA + IMM</t>
+  </si>
+  <si>
+    <t>ANDI RD, RA, IMM</t>
+  </si>
+  <si>
+    <t>RD = RA &amp; IMM</t>
+  </si>
+  <si>
+    <t>LOAD RD, RA, IMM</t>
+  </si>
+  <si>
+    <t>RD = x(RA+IMM)</t>
+  </si>
+  <si>
+    <t>STORE RA, RB, IMM</t>
+  </si>
+  <si>
+    <t>x(RA + IMM) = RB</t>
+  </si>
+  <si>
+    <t>BEQ RA, RB, IMM</t>
+  </si>
+  <si>
+    <t>(signed IMM)</t>
+  </si>
+  <si>
+    <t>BNE RA, RB, IMM</t>
+  </si>
+  <si>
+    <t>JMP RA, IMM</t>
+  </si>
+  <si>
+    <t>PC = RA + IMM</t>
+  </si>
+  <si>
+    <t>HALT IMM</t>
+  </si>
+  <si>
+    <t>JMPA IMM</t>
+  </si>
+  <si>
+    <t>No operation</t>
+  </si>
+  <si>
+    <t>RD = RA</t>
+  </si>
+  <si>
+    <t>RD = 0</t>
+  </si>
+  <si>
+    <t>RD += 1</t>
+  </si>
+  <si>
+    <t>RD -=1</t>
+  </si>
+  <si>
+    <t>RD = 0-RD</t>
+  </si>
+  <si>
+    <t>PC = IMM</t>
+  </si>
+  <si>
+    <t>PC += IMM</t>
+  </si>
+  <si>
+    <t>If RA ~= 0 then PC += IMM</t>
+  </si>
+  <si>
+    <t>If RA == 0 then PC += IMM</t>
+  </si>
+  <si>
+    <t>If RA == RB then PC += IMM</t>
+  </si>
+  <si>
+    <t>If RA ~= RB then PC += IMM</t>
+  </si>
+  <si>
+    <t>Stop execution</t>
+  </si>
+  <si>
+    <t>RD = IMM</t>
+  </si>
+  <si>
+    <t>Instructions:</t>
+  </si>
+  <si>
+    <t>MACROS:</t>
+  </si>
+  <si>
+    <t>Cycle Length</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>NAND</t>
+  </si>
+  <si>
+    <t>XNOR</t>
+  </si>
+  <si>
+    <t>SWAP</t>
+  </si>
+  <si>
+    <t>NOR RD, RA, RB</t>
+  </si>
+  <si>
+    <t>NAND RD, RA, RB</t>
+  </si>
+  <si>
+    <t>XNOR RD, RA, RB</t>
+  </si>
+  <si>
+    <t>SWAP RA, RB</t>
+  </si>
+  <si>
+    <t>RD = ~(RA | RB)</t>
+  </si>
+  <si>
+    <t>RD = ~(RA &amp; RB)</t>
+  </si>
+  <si>
+    <t>RD = ~(RA ^ RB)</t>
+  </si>
+  <si>
+    <t>RA = RB, RB = RA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,6 +511,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -389,9 +544,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -726,26 +882,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3793813-9B20-438F-90FC-3E0D3543C5BE}">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -756,378 +913,588 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="G13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+      <c r="G26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" t="s">
+        <v>129</v>
+      </c>
+      <c r="H28" t="s">
         <v>56</v>
       </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" t="s">
-        <v>80</v>
-      </c>
-      <c r="J7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" t="s">
-        <v>81</v>
-      </c>
-      <c r="J8" t="s">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="D30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="D32" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
+        <v>107</v>
+      </c>
+      <c r="G33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="D36" t="s">
         <v>45</v>
       </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>85</v>
-      </c>
-      <c r="J13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1011</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="1">
-        <v>1100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1110</v>
-      </c>
-      <c r="D21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" t="s">
-        <v>53</v>
-      </c>
-      <c r="I21" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="G36" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="1">
-        <v>1111</v>
-      </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>76</v>
+      <c r="H36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>141</v>
+      </c>
+      <c r="D37" t="s">
+        <v>145</v>
+      </c>
+      <c r="G37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="G38" t="s">
+        <v>150</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" t="s">
+        <v>147</v>
+      </c>
+      <c r="G39" t="s">
+        <v>151</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" t="s">
+        <v>148</v>
+      </c>
+      <c r="G40" t="s">
+        <v>152</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ISA Documentation.xlsx
+++ b/Excel/ISA Documentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ProtoCore\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC67595-03DC-4246-9ACD-EDB97874E690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0744E324-492F-4953-A40E-2C999B72B789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B12F2B8D-ADA6-4D34-B7FA-CEA8D28977FA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="154">
   <si>
     <t>Format:</t>
   </si>
@@ -495,6 +495,9 @@
   </si>
   <si>
     <t>RA = RB, RB = RA</t>
+  </si>
+  <si>
+    <t>.equ can be used to add a symbol to the assembler dictionary, such as substituting R0 with zero using .equ zero, R0</t>
   </si>
 </sst>
 </file>
@@ -882,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3793813-9B20-438F-90FC-3E0D3543C5BE}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -1497,6 +1500,11 @@
         <v>3</v>
       </c>
     </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
